--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T09:32:51+00:00</t>
+    <t>2025-12-16T10:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T10:42:57+00:00</t>
+    <t>2025-12-16T14:19:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:19:48+00:00</t>
+    <t>2025-12-17T08:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-17T08:30:11+00:00</t>
+    <t>2025-12-18T13:34:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-18T13:34:16+00:00</t>
+    <t>2025-12-18T13:56:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-18T13:56:20+00:00</t>
+    <t>2025-12-18T14:24:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-18T14:24:07+00:00</t>
+    <t>2025-12-18T14:41:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-18T14:41:20+00:00</t>
+    <t>2025-12-18T14:51:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-18T14:51:14+00:00</t>
+    <t>2025-12-18T14:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-18T14:53:53+00:00</t>
+    <t>2025-12-18T15:02:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-18T15:02:19+00:00</t>
+    <t>2025-12-18T15:16:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-18T15:16:45+00:00</t>
+    <t>2025-12-18T15:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-18T15:13:32+00:00</t>
+    <t>2025-12-18T15:21:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-18T15:21:25+00:00</t>
+    <t>2026-01-05T14:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-05T14:32:04+00:00</t>
+    <t>2026-01-05T14:41:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-05T14:41:11+00:00</t>
+    <t>2026-01-07T10:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:21:37+00:00</t>
+    <t>2026-01-07T10:28:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.1</t>
+    <t>0.0.1-rc</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:28:01+00:00</t>
+    <t>2026-01-07T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:59:40+00:00</t>
+    <t>2026-01-08T15:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-08T15:50:08+00:00</t>
+    <t>2026-01-12T13:18:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T13:18:56+00:00</t>
+    <t>2026-01-12T13:39:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
